--- a/बजेट माग estimate/thekka/रिमाल घडेरी सिँचाई/रिमाल घडेरी सिँचाई - sir.xlsx
+++ b/बजेट माग estimate/thekka/रिमाल घडेरी सिँचाई/रिमाल घडेरी सिँचाई - sir.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF3D46A0-1404-4DBE-8CEF-B22088C39164}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9E47EF5-CB65-4D22-9076-B3714A10CE6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="53">
   <si>
     <t>Government of Nepal</t>
   </si>
@@ -117,24 +117,9 @@
     <t>Total</t>
   </si>
   <si>
-    <t>Budget allocated</t>
-  </si>
-  <si>
-    <t>Municipal payment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contingencies </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maintanince </t>
-  </si>
-  <si>
     <t>F.Y.: 2082/2083</t>
   </si>
   <si>
-    <t>User contribution</t>
-  </si>
-  <si>
     <t>Length (m)</t>
   </si>
   <si>
@@ -147,27 +132,15 @@
     <t>PS</t>
   </si>
   <si>
-    <t>-13% VAT for sand</t>
-  </si>
-  <si>
     <t>Plain cement concrete (1:2:4)</t>
   </si>
   <si>
-    <t>-13% VAT for cement</t>
-  </si>
-  <si>
-    <t>-13% VAT for aggregate</t>
-  </si>
-  <si>
     <t>sqm</t>
   </si>
   <si>
     <t>length</t>
   </si>
   <si>
-    <t>-13% VAT for block stone</t>
-  </si>
-  <si>
     <t>thickness</t>
   </si>
   <si>
@@ -180,9 +153,6 @@
     <t>Total Weight (Kg)</t>
   </si>
   <si>
-    <t>-13% VAT for nails</t>
-  </si>
-  <si>
     <t>Earthwork in Excavation in ordinary soil</t>
   </si>
   <si>
@@ -195,16 +165,7 @@
     <t>Kg</t>
   </si>
   <si>
-    <t>-13% VAT for MS bars</t>
-  </si>
-  <si>
-    <t>-13% VAT for Bind wire</t>
-  </si>
-  <si>
     <t>Form work for concrete work</t>
-  </si>
-  <si>
-    <t>-13% VAT for local wood</t>
   </si>
   <si>
     <t>breadth</t>
@@ -421,7 +382,7 @@
     <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -535,21 +496,6 @@
     <xf numFmtId="1" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -571,6 +517,12 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1098,7 +1050,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q78"/>
+  <dimension ref="A1:Q59"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.7109375" customWidth="1"/>
@@ -1113,113 +1065,113 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A1" s="52" t="s">
+      <c r="A1" s="47" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
-      <c r="H1" s="52"/>
-      <c r="I1" s="52"/>
-      <c r="J1" s="52"/>
-      <c r="K1" s="52"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="47"/>
+      <c r="J1" s="47"/>
+      <c r="K1" s="47"/>
     </row>
     <row r="2" spans="1:17" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="53" t="s">
+      <c r="A2" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="53"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="53"/>
+      <c r="B2" s="48"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="48"/>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A3" s="54" t="s">
+      <c r="A3" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="54"/>
-      <c r="C3" s="54"/>
-      <c r="D3" s="54"/>
-      <c r="E3" s="54"/>
-      <c r="F3" s="54"/>
-      <c r="G3" s="54"/>
-      <c r="H3" s="54"/>
-      <c r="I3" s="54"/>
-      <c r="J3" s="54"/>
-      <c r="K3" s="54"/>
+      <c r="B3" s="49"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="49"/>
+      <c r="G3" s="49"/>
+      <c r="H3" s="49"/>
+      <c r="I3" s="49"/>
+      <c r="J3" s="49"/>
+      <c r="K3" s="49"/>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" s="54" t="s">
+      <c r="A4" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="54"/>
-      <c r="C4" s="54"/>
-      <c r="D4" s="54"/>
-      <c r="E4" s="54"/>
-      <c r="F4" s="54"/>
-      <c r="G4" s="54"/>
-      <c r="H4" s="54"/>
-      <c r="I4" s="54"/>
-      <c r="J4" s="54"/>
-      <c r="K4" s="54"/>
+      <c r="B4" s="49"/>
+      <c r="C4" s="49"/>
+      <c r="D4" s="49"/>
+      <c r="E4" s="49"/>
+      <c r="F4" s="49"/>
+      <c r="G4" s="49"/>
+      <c r="H4" s="49"/>
+      <c r="I4" s="49"/>
+      <c r="J4" s="49"/>
+      <c r="K4" s="49"/>
     </row>
     <row r="5" spans="1:17" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A5" s="55" t="s">
+      <c r="A5" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="55"/>
-      <c r="C5" s="55"/>
-      <c r="D5" s="55"/>
-      <c r="E5" s="55"/>
-      <c r="F5" s="55"/>
-      <c r="G5" s="55"/>
-      <c r="H5" s="55"/>
-      <c r="I5" s="55"/>
-      <c r="J5" s="55"/>
-      <c r="K5" s="55"/>
+      <c r="B5" s="50"/>
+      <c r="C5" s="50"/>
+      <c r="D5" s="50"/>
+      <c r="E5" s="50"/>
+      <c r="F5" s="50"/>
+      <c r="G5" s="50"/>
+      <c r="H5" s="50"/>
+      <c r="I5" s="50"/>
+      <c r="J5" s="50"/>
+      <c r="K5" s="50"/>
     </row>
     <row r="6" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="56" t="s">
-        <v>64</v>
-      </c>
-      <c r="B6" s="56"/>
-      <c r="C6" s="56"/>
-      <c r="D6" s="56"/>
-      <c r="E6" s="56"/>
-      <c r="F6" s="56"/>
+      <c r="A6" s="51" t="s">
+        <v>51</v>
+      </c>
+      <c r="B6" s="51"/>
+      <c r="C6" s="51"/>
+      <c r="D6" s="51"/>
+      <c r="E6" s="51"/>
+      <c r="F6" s="51"/>
       <c r="G6" s="3"/>
-      <c r="H6" s="57" t="s">
-        <v>25</v>
-      </c>
-      <c r="I6" s="57"/>
-      <c r="J6" s="57"/>
-      <c r="K6" s="57"/>
+      <c r="H6" s="52" t="s">
+        <v>21</v>
+      </c>
+      <c r="I6" s="52"/>
+      <c r="J6" s="52"/>
+      <c r="K6" s="52"/>
     </row>
     <row r="7" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="50" t="s">
-        <v>29</v>
-      </c>
-      <c r="B7" s="50"/>
-      <c r="C7" s="50"/>
-      <c r="D7" s="50"/>
-      <c r="E7" s="50"/>
-      <c r="F7" s="50"/>
+      <c r="A7" s="45" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="45"/>
+      <c r="C7" s="45"/>
+      <c r="D7" s="45"/>
+      <c r="E7" s="45"/>
+      <c r="F7" s="45"/>
       <c r="G7" s="4"/>
-      <c r="H7" s="51" t="s">
-        <v>39</v>
-      </c>
-      <c r="I7" s="51"/>
-      <c r="J7" s="51"/>
-      <c r="K7" s="51"/>
+      <c r="H7" s="46" t="s">
+        <v>30</v>
+      </c>
+      <c r="I7" s="46"/>
+      <c r="J7" s="46"/>
+      <c r="K7" s="46"/>
     </row>
     <row r="8" spans="1:17" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
@@ -1262,7 +1214,7 @@
         <v>1</v>
       </c>
       <c r="B9" s="40" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C9" s="13"/>
       <c r="D9" s="14"/>
@@ -1278,7 +1230,7 @@
     <row r="10" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="16"/>
       <c r="B10" s="17" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="C10" s="18">
         <v>0.5</v>
@@ -1304,7 +1256,7 @@
     <row r="11" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="16"/>
       <c r="B11" s="17" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="C11" s="18">
         <v>1</v>
@@ -1332,7 +1284,7 @@
     <row r="12" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="16"/>
       <c r="B12" s="17" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="C12" s="18">
         <v>0.5</v>
@@ -1346,7 +1298,7 @@
         <v>1.5239256324291375</v>
       </c>
       <c r="F12" s="7">
-        <f>F36</f>
+        <f>F32</f>
         <v>3.047851264858275</v>
       </c>
       <c r="G12" s="7">
@@ -1361,7 +1313,7 @@
     <row r="13" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="C13" s="18">
         <v>0.5</v>
@@ -1375,7 +1327,7 @@
         <v>0.75</v>
       </c>
       <c r="F13" s="7">
-        <f>F37</f>
+        <f>F33</f>
         <v>1.5</v>
       </c>
       <c r="G13" s="7">
@@ -1401,14 +1353,15 @@
         <v>37.723191476223811</v>
       </c>
       <c r="H14" s="24" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="I14" s="2">
-        <v>963.05</v>
+        <f>1.15*963.05</f>
+        <v>1107.5074999999999</v>
       </c>
       <c r="J14" s="25">
         <f>G14*I14</f>
-        <v>36329.319551177337</v>
+        <v>41778.717483853936</v>
       </c>
       <c r="K14" s="23"/>
     </row>
@@ -1430,7 +1383,7 @@
         <v>2</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C16" s="19"/>
       <c r="D16" s="19"/>
@@ -1445,15 +1398,15 @@
     <row r="17" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="16"/>
       <c r="B17" s="17" t="str">
-        <f>B10</f>
+        <f t="shared" ref="B17:D20" si="0">B10</f>
         <v>-for kulo</v>
       </c>
       <c r="C17" s="18">
-        <f>C10</f>
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
       <c r="D17" s="7">
-        <f>D10</f>
+        <f t="shared" si="0"/>
         <v>145</v>
       </c>
       <c r="E17" s="7">
@@ -1474,23 +1427,23 @@
     <row r="18" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="16"/>
       <c r="B18" s="17" t="str">
-        <f>B11</f>
+        <f t="shared" si="0"/>
         <v>- for causeway</v>
       </c>
       <c r="C18" s="18">
-        <f>C11</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D18" s="7">
-        <f>D11</f>
+        <f t="shared" si="0"/>
         <v>3.047851264858275</v>
       </c>
       <c r="E18" s="7">
-        <f>E11</f>
+        <f t="shared" ref="E18:F20" si="1">E11</f>
         <v>3.6574215178299299</v>
       </c>
       <c r="F18" s="7">
-        <f>F11</f>
+        <f t="shared" si="1"/>
         <v>0.15</v>
       </c>
       <c r="G18" s="7">
@@ -1505,23 +1458,23 @@
     <row r="19" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="16"/>
       <c r="B19" s="17" t="str">
-        <f>B12</f>
+        <f t="shared" si="0"/>
         <v>-for masonary wall 1</v>
       </c>
       <c r="C19" s="18">
-        <f>C12</f>
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
       <c r="D19" s="7">
-        <f>D12</f>
+        <f t="shared" si="0"/>
         <v>3.047851264858275</v>
       </c>
       <c r="E19" s="7">
-        <f>E12</f>
+        <f t="shared" si="1"/>
         <v>1.5239256324291375</v>
       </c>
       <c r="F19" s="7">
-        <f>F12</f>
+        <f t="shared" si="1"/>
         <v>3.047851264858275</v>
       </c>
       <c r="G19" s="7">
@@ -1536,23 +1489,23 @@
     <row r="20" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="16"/>
       <c r="B20" s="17" t="str">
-        <f>B13</f>
+        <f t="shared" si="0"/>
         <v>-for masonary wall 2</v>
       </c>
       <c r="C20" s="18">
-        <f>C13</f>
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
       <c r="D20" s="7">
-        <f>D13</f>
+        <f t="shared" si="0"/>
         <v>3.6574215178299299</v>
       </c>
       <c r="E20" s="7">
-        <f>E13</f>
+        <f t="shared" si="1"/>
         <v>0.75</v>
       </c>
       <c r="F20" s="7">
-        <f>F13</f>
+        <f t="shared" si="1"/>
         <v>1.5</v>
       </c>
       <c r="G20" s="7">
@@ -1578,23 +1531,21 @@
         <v>16.788816476223818</v>
       </c>
       <c r="H21" s="24" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="I21" s="2">
-        <f>4493.69</f>
-        <v>4493.6899999999996</v>
+        <f>1.15*4493.69</f>
+        <v>5167.7434999999996</v>
       </c>
       <c r="J21" s="25">
         <f>G21*I21</f>
-        <v>75443.736711042206</v>
+        <v>86760.297217698535</v>
       </c>
       <c r="K21" s="23"/>
     </row>
     <row r="22" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="16"/>
-      <c r="B22" s="17" t="s">
-        <v>37</v>
-      </c>
+      <c r="B22" s="19"/>
       <c r="C22" s="19"/>
       <c r="D22" s="19"/>
       <c r="E22" s="19"/>
@@ -1602,15 +1553,16 @@
       <c r="G22" s="19"/>
       <c r="H22" s="19"/>
       <c r="I22" s="19"/>
-      <c r="J22" s="25">
-        <f>0.13*G21*3091.19</f>
-        <v>6746.6648084079798</v>
-      </c>
+      <c r="J22" s="19"/>
       <c r="K22" s="19"/>
     </row>
     <row r="23" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="16"/>
-      <c r="B23" s="19"/>
+      <c r="A23" s="16">
+        <v>3</v>
+      </c>
+      <c r="B23" s="19" t="s">
+        <v>26</v>
+      </c>
       <c r="C23" s="19"/>
       <c r="D23" s="19"/>
       <c r="E23" s="19"/>
@@ -1622,17 +1574,28 @@
       <c r="K23" s="19"/>
     </row>
     <row r="24" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="16">
-        <v>3</v>
-      </c>
-      <c r="B24" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="C24" s="19"/>
-      <c r="D24" s="19"/>
-      <c r="E24" s="19"/>
-      <c r="F24" s="19"/>
-      <c r="G24" s="19"/>
+      <c r="A24" s="16"/>
+      <c r="B24" s="17" t="str">
+        <f>B17</f>
+        <v>-for kulo</v>
+      </c>
+      <c r="C24" s="18">
+        <f>C17</f>
+        <v>0.5</v>
+      </c>
+      <c r="D24" s="7">
+        <v>145</v>
+      </c>
+      <c r="E24" s="7">
+        <v>0.54999999999999993</v>
+      </c>
+      <c r="F24" s="19">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="G24" s="7">
+        <f>PRODUCT(C24:F24)</f>
+        <v>2.9906249999999992</v>
+      </c>
       <c r="H24" s="19"/>
       <c r="I24" s="19"/>
       <c r="J24" s="19"/>
@@ -1641,25 +1604,28 @@
     <row r="25" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="16"/>
       <c r="B25" s="17" t="str">
-        <f>B17</f>
-        <v>-for kulo</v>
+        <f>B19</f>
+        <v>-for masonary wall 1</v>
       </c>
       <c r="C25" s="18">
-        <f>C17</f>
-        <v>0.5</v>
+        <f>1</f>
+        <v>1</v>
       </c>
       <c r="D25" s="7">
-        <v>145</v>
+        <f>D32</f>
+        <v>3.047851264858275</v>
       </c>
       <c r="E25" s="7">
-        <v>0.54999999999999993</v>
+        <f>F32/2</f>
+        <v>1.5239256324291375</v>
       </c>
       <c r="F25" s="19">
-        <v>7.4999999999999997E-2</v>
+        <f>0.05</f>
+        <v>0.05</v>
       </c>
       <c r="G25" s="7">
         <f>PRODUCT(C25:F25)</f>
-        <v>2.9906249999999992</v>
+        <v>0.23223493331745468</v>
       </c>
       <c r="H25" s="19"/>
       <c r="I25" s="19"/>
@@ -1668,29 +1634,23 @@
     </row>
     <row r="26" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="16"/>
-      <c r="B26" s="17" t="str">
-        <f>B19</f>
-        <v>-for masonary wall 1</v>
-      </c>
+      <c r="B26" s="17"/>
       <c r="C26" s="18">
-        <f>1</f>
         <v>1</v>
       </c>
       <c r="D26" s="7">
-        <f>D36</f>
+        <f>D25</f>
         <v>3.047851264858275</v>
       </c>
-      <c r="E26" s="7">
-        <f>F36/2</f>
-        <v>1.5239256324291375</v>
+      <c r="E26" s="5">
+        <v>0.45</v>
       </c>
       <c r="F26" s="19">
-        <f>0.05</f>
         <v>0.05</v>
       </c>
       <c r="G26" s="7">
         <f>PRODUCT(C26:F26)</f>
-        <v>0.23223493331745468</v>
+        <v>6.8576653459311188E-2</v>
       </c>
       <c r="H26" s="19"/>
       <c r="I26" s="19"/>
@@ -1699,23 +1659,27 @@
     </row>
     <row r="27" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="16"/>
-      <c r="B27" s="17"/>
+      <c r="B27" s="17" t="str">
+        <f>B20</f>
+        <v>-for masonary wall 2</v>
+      </c>
       <c r="C27" s="18">
         <v>1</v>
       </c>
       <c r="D27" s="7">
-        <f>D26</f>
-        <v>3.047851264858275</v>
-      </c>
-      <c r="E27" s="5">
-        <v>0.45</v>
+        <f>D33</f>
+        <v>3.6574215178299299</v>
+      </c>
+      <c r="E27" s="7">
+        <f>F33/2</f>
+        <v>0.75</v>
       </c>
       <c r="F27" s="19">
         <v>0.05</v>
       </c>
       <c r="G27" s="7">
         <f>PRODUCT(C27:F27)</f>
-        <v>6.8576653459311188E-2</v>
+        <v>0.13715330691862238</v>
       </c>
       <c r="H27" s="19"/>
       <c r="I27" s="19"/>
@@ -1724,87 +1688,74 @@
     </row>
     <row r="28" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="16"/>
-      <c r="B28" s="17" t="str">
-        <f>B20</f>
-        <v>-for masonary wall 2</v>
-      </c>
+      <c r="B28" s="17"/>
       <c r="C28" s="18">
         <v>1</v>
       </c>
       <c r="D28" s="7">
-        <f>D37</f>
+        <f>D33</f>
         <v>3.6574215178299299</v>
       </c>
       <c r="E28" s="7">
-        <f>F37/2</f>
-        <v>0.75</v>
+        <v>0.45</v>
       </c>
       <c r="F28" s="19">
         <v>0.05</v>
       </c>
       <c r="G28" s="7">
         <f>PRODUCT(C28:F28)</f>
-        <v>0.13715330691862238</v>
+        <v>8.2291984151173433E-2</v>
       </c>
       <c r="H28" s="19"/>
       <c r="I28" s="19"/>
       <c r="J28" s="19"/>
       <c r="K28" s="19"/>
     </row>
-    <row r="29" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="16"/>
-      <c r="B29" s="17"/>
-      <c r="C29" s="18">
-        <v>1</v>
-      </c>
-      <c r="D29" s="7">
-        <f>D37</f>
-        <v>3.6574215178299299</v>
-      </c>
-      <c r="E29" s="7">
-        <v>0.45</v>
-      </c>
-      <c r="F29" s="19">
-        <v>0.05</v>
-      </c>
-      <c r="G29" s="7">
-        <f>PRODUCT(C29:F29)</f>
-        <v>8.2291984151173433E-2</v>
-      </c>
-      <c r="H29" s="19"/>
-      <c r="I29" s="19"/>
-      <c r="J29" s="19"/>
-      <c r="K29" s="19"/>
-    </row>
-    <row r="30" spans="1:11" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="20"/>
-      <c r="B30" s="21" t="s">
+    <row r="29" spans="1:11" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="20"/>
+      <c r="B29" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="C30" s="22"/>
-      <c r="D30" s="1"/>
-      <c r="E30" s="23"/>
-      <c r="F30" s="23"/>
-      <c r="G30" s="2">
-        <f>SUM(G25:G29)</f>
+      <c r="C29" s="22"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="23"/>
+      <c r="F29" s="23"/>
+      <c r="G29" s="2">
+        <f>SUM(G24:G28)</f>
         <v>3.5108818778465611</v>
       </c>
-      <c r="H30" s="24" t="s">
-        <v>28</v>
-      </c>
-      <c r="I30" s="2">
-        <v>13343.7</v>
-      </c>
-      <c r="J30" s="25">
-        <f>G30*I30</f>
-        <v>46848.154513421163</v>
-      </c>
-      <c r="K30" s="23"/>
-    </row>
-    <row r="31" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="16"/>
-      <c r="B31" s="17" t="s">
-        <v>31</v>
+      <c r="H29" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="I29" s="2">
+        <f>1.15*13343.7</f>
+        <v>15345.254999999999</v>
+      </c>
+      <c r="J29" s="25">
+        <f>G29*I29</f>
+        <v>53875.377690434332</v>
+      </c>
+      <c r="K29" s="23"/>
+    </row>
+    <row r="30" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="16"/>
+      <c r="B30" s="19"/>
+      <c r="C30" s="19"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="19"/>
+      <c r="H30" s="19"/>
+      <c r="I30" s="19"/>
+      <c r="J30" s="19"/>
+      <c r="K30" s="19"/>
+    </row>
+    <row r="31" spans="1:11" s="5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A31" s="16">
+        <v>4</v>
+      </c>
+      <c r="B31" s="26" t="s">
+        <v>41</v>
       </c>
       <c r="C31" s="19"/>
       <c r="D31" s="19"/>
@@ -1813,68 +1764,100 @@
       <c r="G31" s="19"/>
       <c r="H31" s="19"/>
       <c r="I31" s="19"/>
-      <c r="J31" s="25">
-        <f>0.13*G30*1413.27</f>
-        <v>645.03712409554726</v>
-      </c>
+      <c r="J31" s="19"/>
       <c r="K31" s="19"/>
     </row>
     <row r="32" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="16"/>
-      <c r="B32" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="C32" s="19"/>
-      <c r="D32" s="19"/>
-      <c r="E32" s="19"/>
-      <c r="F32" s="19"/>
-      <c r="G32" s="19"/>
+      <c r="B32" s="17" t="str">
+        <f t="shared" ref="B32:D33" si="2">B12</f>
+        <v>-for masonary wall 1</v>
+      </c>
+      <c r="C32" s="18">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="D32" s="7">
+        <f t="shared" si="2"/>
+        <v>3.047851264858275</v>
+      </c>
+      <c r="E32" s="7">
+        <f>((F32/2)+0.45)/2</f>
+        <v>0.98696281621456872</v>
+      </c>
+      <c r="F32" s="7">
+        <f>10/3.281</f>
+        <v>3.047851264858275</v>
+      </c>
+      <c r="G32" s="7">
+        <f>PRODUCT(C32:F32)</f>
+        <v>4.5841448762079526</v>
+      </c>
       <c r="H32" s="19"/>
       <c r="I32" s="19"/>
-      <c r="J32" s="25">
-        <f>0.13*G30*4096</f>
-        <v>1869.4743823157369</v>
-      </c>
+      <c r="J32" s="19"/>
       <c r="K32" s="19"/>
     </row>
     <row r="33" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="16"/>
-      <c r="B33" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="C33" s="19"/>
-      <c r="D33" s="19"/>
-      <c r="E33" s="19"/>
-      <c r="F33" s="19"/>
-      <c r="G33" s="19"/>
+      <c r="B33" s="17" t="str">
+        <f t="shared" si="2"/>
+        <v>-for masonary wall 2</v>
+      </c>
+      <c r="C33" s="18">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="D33" s="7">
+        <f t="shared" si="2"/>
+        <v>3.6574215178299299</v>
+      </c>
+      <c r="E33" s="7">
+        <f>((F33/2)+0.45)/2</f>
+        <v>0.6</v>
+      </c>
+      <c r="F33" s="7">
+        <f>1.5</f>
+        <v>1.5</v>
+      </c>
+      <c r="G33" s="7">
+        <f>PRODUCT(C33:F33)</f>
+        <v>1.6458396830234685</v>
+      </c>
       <c r="H33" s="19"/>
       <c r="I33" s="19"/>
-      <c r="J33" s="25">
-        <f>0.13*G30*(368.76+737.51+1743.21)</f>
-        <v>1300.5444001272085</v>
-      </c>
+      <c r="J33" s="19"/>
       <c r="K33" s="19"/>
     </row>
-    <row r="34" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="16"/>
-      <c r="B34" s="19"/>
-      <c r="C34" s="19"/>
-      <c r="D34" s="19"/>
-      <c r="E34" s="19"/>
-      <c r="F34" s="19"/>
-      <c r="G34" s="19"/>
-      <c r="H34" s="19"/>
-      <c r="I34" s="19"/>
-      <c r="J34" s="19"/>
-      <c r="K34" s="19"/>
-    </row>
-    <row r="35" spans="1:11" s="5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A35" s="16">
-        <v>4</v>
-      </c>
-      <c r="B35" s="26" t="s">
-        <v>54</v>
-      </c>
+    <row r="34" spans="1:11" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="20"/>
+      <c r="B34" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="C34" s="22"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="23"/>
+      <c r="F34" s="23"/>
+      <c r="G34" s="2">
+        <f>SUM(G32:G33)</f>
+        <v>6.2299845592314211</v>
+      </c>
+      <c r="H34" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="I34" s="2">
+        <f>1.15*12225.55</f>
+        <v>14059.382499999998</v>
+      </c>
+      <c r="J34" s="25">
+        <f>G34*I34</f>
+        <v>87589.735887328439</v>
+      </c>
+      <c r="K34" s="23"/>
+    </row>
+    <row r="35" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="16"/>
+      <c r="B35" s="19"/>
       <c r="C35" s="19"/>
       <c r="D35" s="19"/>
       <c r="E35" s="19"/>
@@ -1886,31 +1869,17 @@
       <c r="K35" s="19"/>
     </row>
     <row r="36" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="16"/>
-      <c r="B36" s="17" t="str">
-        <f>B12</f>
-        <v>-for masonary wall 1</v>
-      </c>
-      <c r="C36" s="18">
-        <f>C12</f>
-        <v>0.5</v>
-      </c>
-      <c r="D36" s="7">
-        <f>D12</f>
-        <v>3.047851264858275</v>
-      </c>
-      <c r="E36" s="7">
-        <f>((F36/2)+0.45)/2</f>
-        <v>0.98696281621456872</v>
-      </c>
-      <c r="F36" s="7">
-        <f>10/3.281</f>
-        <v>3.047851264858275</v>
-      </c>
-      <c r="G36" s="7">
-        <f>PRODUCT(C36:F36)</f>
-        <v>4.5841448762079526</v>
-      </c>
+      <c r="A36" s="16">
+        <v>5</v>
+      </c>
+      <c r="B36" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="C36" s="19"/>
+      <c r="D36" s="19"/>
+      <c r="E36" s="19"/>
+      <c r="F36" s="19"/>
+      <c r="G36" s="19"/>
       <c r="H36" s="19"/>
       <c r="I36" s="19"/>
       <c r="J36" s="19"/>
@@ -1919,28 +1888,25 @@
     <row r="37" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="16"/>
       <c r="B37" s="17" t="str">
-        <f>B13</f>
-        <v>-for masonary wall 2</v>
-      </c>
-      <c r="C37" s="18">
-        <f>C13</f>
-        <v>0.5</v>
+        <f>B42</f>
+        <v>-for kulo shear wall</v>
+      </c>
+      <c r="C37" s="19">
+        <f>C42*2</f>
+        <v>4</v>
       </c>
       <c r="D37" s="7">
-        <f>D13</f>
-        <v>3.6574215178299299</v>
-      </c>
-      <c r="E37" s="7">
-        <f>((F37/2)+0.45)/2</f>
-        <v>0.6</v>
-      </c>
+        <f>D42</f>
+        <v>145</v>
+      </c>
+      <c r="E37" s="7"/>
       <c r="F37" s="7">
-        <f>1.5</f>
-        <v>1.5</v>
+        <f>F42</f>
+        <v>0.35</v>
       </c>
       <c r="G37" s="7">
         <f>PRODUCT(C37:F37)</f>
-        <v>1.6458396830234685</v>
+        <v>203</v>
       </c>
       <c r="H37" s="19"/>
       <c r="I37" s="19"/>
@@ -1957,26 +1923,25 @@
       <c r="E38" s="23"/>
       <c r="F38" s="23"/>
       <c r="G38" s="2">
-        <f>SUM(G36:G37)</f>
-        <v>6.2299845592314211</v>
+        <f>SUM(G37:G37)</f>
+        <v>203</v>
       </c>
       <c r="H38" s="24" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I38" s="2">
-        <v>12225.55</v>
+        <f>1.15*11188.35/10</f>
+        <v>1286.6602499999999</v>
       </c>
       <c r="J38" s="25">
         <f>G38*I38</f>
-        <v>76164.987728111693</v>
+        <v>261192.03074999998</v>
       </c>
       <c r="K38" s="23"/>
     </row>
     <row r="39" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="16"/>
-      <c r="B39" s="17" t="s">
-        <v>31</v>
-      </c>
+      <c r="B39" s="19"/>
       <c r="C39" s="19"/>
       <c r="D39" s="19"/>
       <c r="E39" s="19"/>
@@ -1984,16 +1949,15 @@
       <c r="G39" s="19"/>
       <c r="H39" s="19"/>
       <c r="I39" s="19"/>
-      <c r="J39" s="25">
-        <f>0.13*G38*1492.66</f>
-        <v>1208.9023377837086</v>
-      </c>
+      <c r="J39" s="19"/>
       <c r="K39" s="19"/>
     </row>
     <row r="40" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="16"/>
-      <c r="B40" s="17" t="s">
-        <v>33</v>
+      <c r="A40" s="16">
+        <v>6</v>
+      </c>
+      <c r="B40" s="19" t="s">
+        <v>34</v>
       </c>
       <c r="C40" s="19"/>
       <c r="D40" s="19"/>
@@ -2002,295 +1966,345 @@
       <c r="G40" s="19"/>
       <c r="H40" s="19"/>
       <c r="I40" s="19"/>
-      <c r="J40" s="25">
-        <f>0.13*G38*1356.8</f>
-        <v>1098.869596495475</v>
-      </c>
+      <c r="J40" s="19"/>
       <c r="K40" s="19"/>
     </row>
     <row r="41" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="16"/>
       <c r="B41" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C41" s="19"/>
-      <c r="D41" s="19"/>
-      <c r="E41" s="19"/>
-      <c r="F41" s="19"/>
-      <c r="G41" s="19"/>
+        <v>44</v>
+      </c>
+      <c r="C41" s="18">
+        <f>C24</f>
+        <v>0.5</v>
+      </c>
+      <c r="D41" s="7">
+        <f>D24</f>
+        <v>145</v>
+      </c>
+      <c r="E41" s="7">
+        <f>E24</f>
+        <v>0.54999999999999993</v>
+      </c>
+      <c r="F41" s="7">
+        <v>0.1</v>
+      </c>
+      <c r="G41" s="7">
+        <f>PRODUCT(C41:F41)</f>
+        <v>3.9874999999999994</v>
+      </c>
       <c r="H41" s="19"/>
       <c r="I41" s="19"/>
-      <c r="J41" s="25">
-        <f>0.13*G38*2833.59</f>
-        <v>2294.9188531350333</v>
-      </c>
+      <c r="J41" s="19"/>
       <c r="K41" s="19"/>
     </row>
     <row r="42" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="16"/>
-      <c r="B42" s="19"/>
-      <c r="C42" s="19"/>
-      <c r="D42" s="19"/>
-      <c r="E42" s="19"/>
-      <c r="F42" s="19"/>
-      <c r="G42" s="19"/>
+      <c r="B42" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="C42" s="18">
+        <v>2</v>
+      </c>
+      <c r="D42" s="7">
+        <v>145</v>
+      </c>
+      <c r="E42" s="7">
+        <v>0.1</v>
+      </c>
+      <c r="F42" s="7">
+        <v>0.35</v>
+      </c>
+      <c r="G42" s="7">
+        <f>PRODUCT(C42:F42)</f>
+        <v>10.149999999999999</v>
+      </c>
       <c r="H42" s="19"/>
       <c r="I42" s="19"/>
       <c r="J42" s="19"/>
       <c r="K42" s="19"/>
     </row>
     <row r="43" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="16">
-        <v>5</v>
-      </c>
-      <c r="B43" s="19" t="s">
-        <v>49</v>
-      </c>
-      <c r="C43" s="19"/>
-      <c r="D43" s="19"/>
-      <c r="E43" s="19"/>
-      <c r="F43" s="19"/>
-      <c r="G43" s="19"/>
+      <c r="A43" s="16"/>
+      <c r="B43" s="17" t="str">
+        <f>B18</f>
+        <v>- for causeway</v>
+      </c>
+      <c r="C43" s="18">
+        <v>1</v>
+      </c>
+      <c r="D43" s="7">
+        <f>D11</f>
+        <v>3.047851264858275</v>
+      </c>
+      <c r="E43" s="7">
+        <f>E11</f>
+        <v>3.6574215178299299</v>
+      </c>
+      <c r="F43" s="7">
+        <f>F11</f>
+        <v>0.15</v>
+      </c>
+      <c r="G43" s="7">
+        <f>PRODUCT(C43:F43)</f>
+        <v>1.6720915198856736</v>
+      </c>
       <c r="H43" s="19"/>
       <c r="I43" s="19"/>
       <c r="J43" s="19"/>
       <c r="K43" s="19"/>
     </row>
-    <row r="44" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="16"/>
-      <c r="B44" s="17" t="str">
-        <f>B51</f>
-        <v>-for kulo shear wall</v>
-      </c>
-      <c r="C44" s="19">
-        <f>C51*2</f>
-        <v>4</v>
-      </c>
-      <c r="D44" s="7">
-        <f>D51</f>
-        <v>145</v>
-      </c>
-      <c r="E44" s="7"/>
-      <c r="F44" s="7">
-        <f>F51</f>
-        <v>0.35</v>
-      </c>
-      <c r="G44" s="7">
-        <f>PRODUCT(C44:F44)</f>
-        <v>203</v>
-      </c>
-      <c r="H44" s="19"/>
-      <c r="I44" s="19"/>
-      <c r="J44" s="19"/>
-      <c r="K44" s="19"/>
-    </row>
-    <row r="45" spans="1:11" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="20"/>
-      <c r="B45" s="21" t="s">
+    <row r="44" spans="1:11" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="20"/>
+      <c r="B44" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="C45" s="22"/>
-      <c r="D45" s="1"/>
-      <c r="E45" s="23"/>
-      <c r="F45" s="23"/>
-      <c r="G45" s="2">
-        <f>SUM(G44:G44)</f>
-        <v>203</v>
-      </c>
-      <c r="H45" s="24" t="s">
+      <c r="C44" s="22"/>
+      <c r="D44" s="1"/>
+      <c r="E44" s="23"/>
+      <c r="F44" s="23"/>
+      <c r="G44" s="2">
+        <f>SUM(G41:G43)</f>
+        <v>15.809591519885672</v>
+      </c>
+      <c r="H44" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="I44" s="2">
+        <f>1.15*14337.7</f>
+        <v>16488.355</v>
+      </c>
+      <c r="J44" s="25">
+        <f>G44*I44</f>
+        <v>260674.15738486449</v>
+      </c>
+      <c r="K44" s="23"/>
+    </row>
+    <row r="45" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="16"/>
+      <c r="B45" s="19"/>
+      <c r="C45" s="19"/>
+      <c r="D45" s="19"/>
+      <c r="E45" s="19"/>
+      <c r="F45" s="19"/>
+      <c r="G45" s="19"/>
+      <c r="H45" s="19"/>
+      <c r="I45" s="19"/>
+      <c r="J45" s="19"/>
+      <c r="K45" s="19"/>
+    </row>
+    <row r="46" spans="1:11" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A46" s="16">
+        <v>7</v>
+      </c>
+      <c r="B46" s="34" t="s">
         <v>35</v>
       </c>
-      <c r="I45" s="2">
-        <f>11188.35/10</f>
-        <v>1118.835</v>
-      </c>
-      <c r="J45" s="25">
-        <f>G45*I45</f>
-        <v>227123.505</v>
-      </c>
-      <c r="K45" s="23"/>
-    </row>
-    <row r="46" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="16"/>
-      <c r="B46" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="C46" s="19"/>
-      <c r="D46" s="19"/>
-      <c r="E46" s="19"/>
-      <c r="F46" s="19"/>
-      <c r="G46" s="19"/>
-      <c r="H46" s="19"/>
-      <c r="I46" s="19"/>
-      <c r="J46" s="25">
-        <f>0.13*G45*6314/10</f>
-        <v>16662.646000000001</v>
-      </c>
-      <c r="K46" s="19"/>
+      <c r="C46" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="D46" s="41" t="s">
+        <v>22</v>
+      </c>
+      <c r="E46" s="41" t="s">
+        <v>31</v>
+      </c>
+      <c r="F46" s="41" t="s">
+        <v>32</v>
+      </c>
+      <c r="G46" s="34"/>
+      <c r="H46" s="34"/>
+      <c r="I46" s="34"/>
+      <c r="J46" s="34"/>
+      <c r="K46" s="34"/>
     </row>
     <row r="47" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="16"/>
-      <c r="B47" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="C47" s="19"/>
-      <c r="D47" s="19"/>
-      <c r="E47" s="19"/>
-      <c r="F47" s="19"/>
-      <c r="G47" s="19"/>
+      <c r="B47" s="17" t="str">
+        <f>B24</f>
+        <v>-for kulo</v>
+      </c>
+      <c r="C47" s="19">
+        <v>967</v>
+      </c>
+      <c r="D47" s="7">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="E47" s="7">
+        <f>10*10/162</f>
+        <v>0.61728395061728392</v>
+      </c>
+      <c r="F47" s="7">
+        <f>PRODUCT(C47:E47)</f>
+        <v>686.45061728395058</v>
+      </c>
+      <c r="G47" s="7">
+        <f>F47</f>
+        <v>686.45061728395058</v>
+      </c>
       <c r="H47" s="19"/>
       <c r="I47" s="19"/>
-      <c r="J47" s="25">
-        <f>0.13*G45*330/10</f>
-        <v>870.87000000000012</v>
-      </c>
+      <c r="J47" s="19"/>
       <c r="K47" s="19"/>
     </row>
     <row r="48" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="16"/>
-      <c r="B48" s="19"/>
-      <c r="C48" s="19"/>
-      <c r="D48" s="19"/>
-      <c r="E48" s="19"/>
-      <c r="F48" s="19"/>
-      <c r="G48" s="19"/>
+      <c r="B48" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C48" s="19">
+        <v>10</v>
+      </c>
+      <c r="D48" s="7">
+        <v>144.9</v>
+      </c>
+      <c r="E48" s="7">
+        <f>10*10/162</f>
+        <v>0.61728395061728392</v>
+      </c>
+      <c r="F48" s="7">
+        <f>PRODUCT(C48:E48)</f>
+        <v>894.44444444444434</v>
+      </c>
+      <c r="G48" s="7">
+        <f>F48</f>
+        <v>894.44444444444434</v>
+      </c>
       <c r="H48" s="19"/>
       <c r="I48" s="19"/>
       <c r="J48" s="19"/>
       <c r="K48" s="19"/>
     </row>
-    <row r="49" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="16">
-        <v>6</v>
-      </c>
-      <c r="B49" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="C49" s="19"/>
-      <c r="D49" s="19"/>
-      <c r="E49" s="19"/>
-      <c r="F49" s="19"/>
-      <c r="G49" s="19"/>
+    <row r="49" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="16"/>
+      <c r="B49" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="C49" s="19">
+        <f>TRUNC((D50)/0.15,0)</f>
+        <v>23</v>
+      </c>
+      <c r="D49" s="7">
+        <f>D43-0.1</f>
+        <v>2.9478512648582749</v>
+      </c>
+      <c r="E49" s="7">
+        <f>10*10/162</f>
+        <v>0.61728395061728392</v>
+      </c>
+      <c r="F49" s="7">
+        <f>PRODUCT(C49:E49)</f>
+        <v>41.852209315889084</v>
+      </c>
+      <c r="G49" s="7">
+        <f>F49</f>
+        <v>41.852209315889084</v>
+      </c>
       <c r="H49" s="19"/>
       <c r="I49" s="19"/>
       <c r="J49" s="19"/>
       <c r="K49" s="19"/>
     </row>
-    <row r="50" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="16"/>
-      <c r="B50" s="17" t="s">
-        <v>57</v>
-      </c>
-      <c r="C50" s="18">
-        <f>C25</f>
-        <v>0.5</v>
+      <c r="B50" s="17"/>
+      <c r="C50" s="19">
+        <f>TRUNC((D49)/0.15,0)</f>
+        <v>19</v>
       </c>
       <c r="D50" s="7">
-        <f>D25</f>
-        <v>145</v>
+        <f>E43-0.1</f>
+        <v>3.5574215178299298</v>
       </c>
       <c r="E50" s="7">
-        <f>E25</f>
-        <v>0.54999999999999993</v>
+        <f>10*10/162</f>
+        <v>0.61728395061728392</v>
       </c>
       <c r="F50" s="7">
-        <v>0.1</v>
+        <f>PRODUCT(C50:E50)</f>
+        <v>41.722844962202871</v>
       </c>
       <c r="G50" s="7">
-        <f>PRODUCT(C50:F50)</f>
-        <v>3.9874999999999994</v>
+        <f>F50</f>
+        <v>41.722844962202871</v>
       </c>
       <c r="H50" s="19"/>
       <c r="I50" s="19"/>
       <c r="J50" s="19"/>
       <c r="K50" s="19"/>
     </row>
-    <row r="51" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="16"/>
-      <c r="B51" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="C51" s="18">
-        <v>2</v>
-      </c>
-      <c r="D51" s="7">
-        <v>145</v>
-      </c>
-      <c r="E51" s="7">
-        <v>0.1</v>
-      </c>
-      <c r="F51" s="7">
-        <v>0.35</v>
-      </c>
-      <c r="G51" s="7">
-        <f>PRODUCT(C51:F51)</f>
-        <v>10.149999999999999</v>
-      </c>
-      <c r="H51" s="19"/>
-      <c r="I51" s="19"/>
-      <c r="J51" s="19"/>
-      <c r="K51" s="19"/>
-    </row>
-    <row r="52" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:17" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="20"/>
+      <c r="B51" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="C51" s="22"/>
+      <c r="D51" s="1"/>
+      <c r="E51" s="23"/>
+      <c r="F51" s="23"/>
+      <c r="G51" s="2">
+        <f>SUM(G47:G50)</f>
+        <v>1664.4701160064867</v>
+      </c>
+      <c r="H51" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="I51" s="2">
+        <f>1.15*9831.6/100</f>
+        <v>113.0634</v>
+      </c>
+      <c r="J51" s="25">
+        <f>G51*I51</f>
+        <v>188190.65051408781</v>
+      </c>
+      <c r="K51" s="23"/>
+    </row>
+    <row r="52" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="16"/>
-      <c r="B52" s="17" t="str">
-        <f>B18</f>
-        <v>- for causeway</v>
-      </c>
-      <c r="C52" s="18">
-        <v>1</v>
-      </c>
-      <c r="D52" s="7">
-        <f>D11</f>
-        <v>3.047851264858275</v>
-      </c>
-      <c r="E52" s="7">
-        <f>E11</f>
-        <v>3.6574215178299299</v>
-      </c>
-      <c r="F52" s="7">
-        <f>F11</f>
-        <v>0.15</v>
-      </c>
-      <c r="G52" s="7">
-        <f>PRODUCT(C52:F52)</f>
-        <v>1.6720915198856736</v>
-      </c>
+      <c r="B52" s="19"/>
+      <c r="C52" s="19"/>
+      <c r="D52" s="19"/>
+      <c r="E52" s="19"/>
+      <c r="F52" s="19"/>
+      <c r="G52" s="19"/>
       <c r="H52" s="19"/>
       <c r="I52" s="19"/>
       <c r="J52" s="19"/>
       <c r="K52" s="19"/>
     </row>
-    <row r="53" spans="1:11" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="20"/>
-      <c r="B53" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="C53" s="22"/>
+    <row r="53" spans="1:17" s="8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A53" s="20">
+        <v>8</v>
+      </c>
+      <c r="B53" s="42" t="s">
+        <v>50</v>
+      </c>
+      <c r="C53" s="22">
+        <v>1</v>
+      </c>
       <c r="D53" s="1"/>
       <c r="E53" s="23"/>
       <c r="F53" s="23"/>
-      <c r="G53" s="2">
-        <f>SUM(G50:G52)</f>
-        <v>15.809591519885672</v>
+      <c r="G53" s="43">
+        <f>PRODUCT(C53:F53)</f>
+        <v>1</v>
       </c>
       <c r="H53" s="24" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="I53" s="2">
-        <v>14337.7</v>
-      </c>
-      <c r="J53" s="25">
+        <v>5000</v>
+      </c>
+      <c r="J53" s="43">
         <f>G53*I53</f>
-        <v>226673.18033466479</v>
+        <v>5000</v>
       </c>
       <c r="K53" s="23"/>
-    </row>
-    <row r="54" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Q53" s="5"/>
+    </row>
+    <row r="54" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="16"/>
-      <c r="B54" s="17" t="s">
-        <v>33</v>
-      </c>
+      <c r="B54" s="40"/>
       <c r="C54" s="19"/>
       <c r="D54" s="19"/>
       <c r="E54" s="19"/>
@@ -2298,470 +2312,94 @@
       <c r="G54" s="19"/>
       <c r="H54" s="19"/>
       <c r="I54" s="19"/>
-      <c r="J54" s="25">
-        <f>0.13*G53*5120</f>
-        <v>10522.864115635903</v>
-      </c>
+      <c r="J54" s="19"/>
       <c r="K54" s="19"/>
     </row>
-    <row r="55" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="16"/>
-      <c r="B55" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="C55" s="19"/>
-      <c r="D55" s="19"/>
-      <c r="E55" s="19"/>
-      <c r="F55" s="19"/>
-      <c r="G55" s="19"/>
-      <c r="H55" s="19"/>
-      <c r="I55" s="19"/>
-      <c r="J55" s="25">
-        <f>0.13*G53*1349.75</f>
-        <v>2774.0695000155388</v>
-      </c>
-      <c r="K55" s="19"/>
-    </row>
-    <row r="56" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="16"/>
-      <c r="B56" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="C56" s="19"/>
-      <c r="D56" s="19"/>
-      <c r="E56" s="19"/>
-      <c r="F56" s="19"/>
-      <c r="G56" s="19"/>
-      <c r="H56" s="19"/>
-      <c r="I56" s="19"/>
-      <c r="J56" s="25">
-        <f>0.13*G53*(972.17+1910.82)</f>
-        <v>5925.2562532689744</v>
-      </c>
-      <c r="K56" s="19"/>
-    </row>
-    <row r="57" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="16"/>
-      <c r="B57" s="19"/>
-      <c r="C57" s="19"/>
-      <c r="D57" s="19"/>
-      <c r="E57" s="19"/>
-      <c r="F57" s="19"/>
-      <c r="G57" s="19"/>
-      <c r="H57" s="19"/>
-      <c r="I57" s="19"/>
-      <c r="J57" s="19"/>
-      <c r="K57" s="19"/>
-    </row>
-    <row r="58" spans="1:11" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A58" s="16">
-        <v>7</v>
-      </c>
-      <c r="B58" s="34" t="s">
-        <v>45</v>
-      </c>
-      <c r="C58" s="34" t="s">
-        <v>7</v>
-      </c>
-      <c r="D58" s="41" t="s">
-        <v>27</v>
-      </c>
-      <c r="E58" s="41" t="s">
-        <v>40</v>
-      </c>
-      <c r="F58" s="41" t="s">
-        <v>41</v>
-      </c>
-      <c r="G58" s="34"/>
-      <c r="H58" s="34"/>
-      <c r="I58" s="34"/>
-      <c r="J58" s="34"/>
-      <c r="K58" s="34"/>
-    </row>
-    <row r="59" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="16"/>
-      <c r="B59" s="17" t="str">
-        <f>B25</f>
-        <v>-for kulo</v>
-      </c>
-      <c r="C59" s="19">
-        <v>967</v>
-      </c>
-      <c r="D59" s="7">
-        <v>1.1499999999999999</v>
-      </c>
-      <c r="E59" s="7">
-        <f>10*10/162</f>
-        <v>0.61728395061728392</v>
-      </c>
-      <c r="F59" s="7">
-        <f>PRODUCT(C59:E59)</f>
-        <v>686.45061728395058</v>
-      </c>
-      <c r="G59" s="7">
-        <f>F59</f>
-        <v>686.45061728395058</v>
-      </c>
-      <c r="H59" s="19"/>
-      <c r="I59" s="19"/>
-      <c r="J59" s="19"/>
-      <c r="K59" s="19"/>
-    </row>
-    <row r="60" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="16"/>
-      <c r="B60" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="C60" s="19">
-        <v>10</v>
-      </c>
-      <c r="D60" s="7">
-        <v>144.9</v>
-      </c>
-      <c r="E60" s="7">
-        <f>10*10/162</f>
-        <v>0.61728395061728392</v>
-      </c>
-      <c r="F60" s="7">
-        <f>PRODUCT(C60:E60)</f>
-        <v>894.44444444444434</v>
-      </c>
-      <c r="G60" s="7">
-        <f>F60</f>
-        <v>894.44444444444434</v>
-      </c>
-      <c r="H60" s="19"/>
-      <c r="I60" s="19"/>
-      <c r="J60" s="19"/>
-      <c r="K60" s="19"/>
-    </row>
-    <row r="61" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="16"/>
-      <c r="B61" s="17" t="s">
-        <v>65</v>
-      </c>
-      <c r="C61" s="19">
-        <f>TRUNC((D62)/0.15,0)</f>
-        <v>23</v>
-      </c>
-      <c r="D61" s="7">
-        <f>D52-0.1</f>
-        <v>2.9478512648582749</v>
-      </c>
-      <c r="E61" s="7">
-        <f>10*10/162</f>
-        <v>0.61728395061728392</v>
-      </c>
-      <c r="F61" s="7">
-        <f>PRODUCT(C61:E61)</f>
-        <v>41.852209315889084</v>
-      </c>
-      <c r="G61" s="7">
-        <f>F61</f>
-        <v>41.852209315889084</v>
-      </c>
-      <c r="H61" s="19"/>
-      <c r="I61" s="19"/>
-      <c r="J61" s="19"/>
-      <c r="K61" s="19"/>
-    </row>
-    <row r="62" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="16"/>
-      <c r="B62" s="17"/>
-      <c r="C62" s="19">
-        <f>TRUNC((D61)/0.15,0)</f>
+    <row r="55" spans="1:17" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="20">
+        <v>9</v>
+      </c>
+      <c r="B55" s="44" t="s">
+        <v>17</v>
+      </c>
+      <c r="C55" s="22">
+        <v>1</v>
+      </c>
+      <c r="D55" s="1"/>
+      <c r="E55" s="23"/>
+      <c r="F55" s="23"/>
+      <c r="G55" s="24">
+        <f>PRODUCT(C55:F55)</f>
+        <v>1</v>
+      </c>
+      <c r="H55" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="I55" s="2">
+        <v>500</v>
+      </c>
+      <c r="J55" s="24">
+        <f>G55*I55</f>
+        <v>500</v>
+      </c>
+      <c r="K55" s="23"/>
+    </row>
+    <row r="56" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="20"/>
+      <c r="B56" s="27"/>
+      <c r="C56" s="22"/>
+      <c r="D56" s="1"/>
+      <c r="E56" s="23"/>
+      <c r="F56" s="23"/>
+      <c r="G56" s="2"/>
+      <c r="H56" s="24"/>
+      <c r="I56" s="2"/>
+      <c r="J56" s="25"/>
+      <c r="K56" s="23"/>
+    </row>
+    <row r="57" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="28"/>
+      <c r="B57" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="C57" s="30"/>
+      <c r="D57" s="31"/>
+      <c r="E57" s="31"/>
+      <c r="F57" s="31"/>
+      <c r="G57" s="25"/>
+      <c r="H57" s="25"/>
+      <c r="I57" s="25"/>
+      <c r="J57" s="25">
+        <f>SUM(J10:J55)</f>
+        <v>985560.96692826762</v>
+      </c>
+      <c r="K57" s="32"/>
+    </row>
+    <row r="58" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Q58" s="6"/>
+    </row>
+    <row r="59" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="33"/>
+      <c r="B59" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="D62" s="7">
-        <f>E52-0.1</f>
-        <v>3.5574215178299298</v>
-      </c>
-      <c r="E62" s="7">
-        <f>10*10/162</f>
-        <v>0.61728395061728392</v>
-      </c>
-      <c r="F62" s="7">
-        <f>PRODUCT(C62:E62)</f>
-        <v>41.722844962202871</v>
-      </c>
-      <c r="G62" s="7">
-        <f>F62</f>
-        <v>41.722844962202871</v>
-      </c>
-      <c r="H62" s="19"/>
-      <c r="I62" s="19"/>
-      <c r="J62" s="19"/>
-      <c r="K62" s="19"/>
-    </row>
-    <row r="63" spans="1:11" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="20"/>
-      <c r="B63" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="C63" s="22"/>
-      <c r="D63" s="1"/>
-      <c r="E63" s="23"/>
-      <c r="F63" s="23"/>
-      <c r="G63" s="2">
-        <f>SUM(G59:G62)</f>
-        <v>1664.4701160064867</v>
-      </c>
-      <c r="H63" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="I63" s="2">
-        <f>9831.6/100</f>
-        <v>98.316000000000003</v>
-      </c>
-      <c r="J63" s="25">
-        <f>G63*I63</f>
-        <v>163644.04392529375</v>
-      </c>
-      <c r="K63" s="23"/>
-    </row>
-    <row r="64" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="16"/>
-      <c r="B64" s="17" t="s">
-        <v>47</v>
-      </c>
-      <c r="C64" s="19"/>
-      <c r="D64" s="19"/>
-      <c r="E64" s="19"/>
-      <c r="F64" s="19"/>
-      <c r="G64" s="19"/>
-      <c r="H64" s="19"/>
-      <c r="I64" s="19"/>
-      <c r="J64" s="25">
-        <f>0.13*G63*9450/100</f>
-        <v>20448.01537513969</v>
-      </c>
-      <c r="K64" s="19"/>
-    </row>
-    <row r="65" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="16"/>
-      <c r="B65" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="C65" s="19"/>
-      <c r="D65" s="19"/>
-      <c r="E65" s="19"/>
-      <c r="F65" s="19"/>
-      <c r="G65" s="19"/>
-      <c r="H65" s="19"/>
-      <c r="I65" s="19"/>
-      <c r="J65" s="25">
-        <f>0.13*G63*120/100</f>
-        <v>259.65733809701192</v>
-      </c>
-      <c r="K65" s="19"/>
-    </row>
-    <row r="66" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="16"/>
-      <c r="B66" s="19"/>
-      <c r="C66" s="19"/>
-      <c r="D66" s="19"/>
-      <c r="E66" s="19"/>
-      <c r="F66" s="19"/>
-      <c r="G66" s="19"/>
-      <c r="H66" s="19"/>
-      <c r="I66" s="19"/>
-      <c r="J66" s="19"/>
-      <c r="K66" s="19"/>
-    </row>
-    <row r="67" spans="1:17" s="8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A67" s="20">
-        <v>8</v>
-      </c>
-      <c r="B67" s="42" t="s">
-        <v>63</v>
-      </c>
-      <c r="C67" s="22">
-        <v>1</v>
-      </c>
-      <c r="D67" s="1"/>
-      <c r="E67" s="23"/>
-      <c r="F67" s="23"/>
-      <c r="G67" s="43">
-        <f>PRODUCT(C67:F67)</f>
-        <v>1</v>
-      </c>
-      <c r="H67" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="I67" s="2">
-        <v>5000</v>
-      </c>
-      <c r="J67" s="43">
-        <f>G67*I67</f>
-        <v>5000</v>
-      </c>
-      <c r="K67" s="23"/>
-      <c r="Q67" s="5"/>
-    </row>
-    <row r="68" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="16"/>
-      <c r="B68" s="40"/>
-      <c r="C68" s="19"/>
-      <c r="D68" s="19"/>
-      <c r="E68" s="19"/>
-      <c r="F68" s="19"/>
-      <c r="G68" s="19"/>
-      <c r="H68" s="19"/>
-      <c r="I68" s="19"/>
-      <c r="J68" s="19"/>
-      <c r="K68" s="19"/>
-    </row>
-    <row r="69" spans="1:17" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="20">
-        <v>9</v>
-      </c>
-      <c r="B69" s="44" t="s">
-        <v>17</v>
-      </c>
-      <c r="C69" s="22">
-        <v>1</v>
-      </c>
-      <c r="D69" s="1"/>
-      <c r="E69" s="23"/>
-      <c r="F69" s="23"/>
-      <c r="G69" s="24">
-        <f>PRODUCT(C69:F69)</f>
-        <v>1</v>
-      </c>
-      <c r="H69" s="24" t="s">
-        <v>18</v>
-      </c>
-      <c r="I69" s="2">
-        <v>500</v>
-      </c>
-      <c r="J69" s="24">
-        <f>G69*I69</f>
-        <v>500</v>
-      </c>
-      <c r="K69" s="23"/>
-    </row>
-    <row r="70" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="20"/>
-      <c r="B70" s="27"/>
-      <c r="C70" s="22"/>
-      <c r="D70" s="1"/>
-      <c r="E70" s="23"/>
-      <c r="F70" s="23"/>
-      <c r="G70" s="2"/>
-      <c r="H70" s="24"/>
-      <c r="I70" s="2"/>
-      <c r="J70" s="25"/>
-      <c r="K70" s="23"/>
-    </row>
-    <row r="71" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="28"/>
-      <c r="B71" s="29" t="s">
-        <v>20</v>
-      </c>
-      <c r="C71" s="30"/>
-      <c r="D71" s="31"/>
-      <c r="E71" s="31"/>
-      <c r="F71" s="31"/>
-      <c r="G71" s="25"/>
-      <c r="H71" s="25"/>
-      <c r="I71" s="25"/>
-      <c r="J71" s="25">
-        <f>SUM(J10:J69)</f>
-        <v>930354.71784822864</v>
-      </c>
-      <c r="K71" s="32"/>
-    </row>
-    <row r="72" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="Q72" s="6"/>
-    </row>
-    <row r="73" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="33"/>
-      <c r="B73" s="34" t="s">
-        <v>19</v>
-      </c>
-      <c r="C73" s="45">
-        <f>J71</f>
-        <v>930354.71784822864</v>
-      </c>
-      <c r="D73" s="46"/>
-      <c r="E73" s="35">
-        <v>100</v>
-      </c>
-      <c r="F73" s="33"/>
-      <c r="G73" s="36"/>
-      <c r="H73" s="33"/>
-      <c r="I73" s="37"/>
-      <c r="J73" s="38"/>
-      <c r="K73" s="39"/>
-      <c r="Q73" s="5"/>
-    </row>
-    <row r="74" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B74" s="34" t="s">
-        <v>21</v>
-      </c>
-      <c r="C74" s="47">
-        <v>820000</v>
-      </c>
-      <c r="D74" s="48"/>
-      <c r="E74" s="35"/>
-    </row>
-    <row r="75" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B75" s="34" t="s">
-        <v>22</v>
-      </c>
-      <c r="C75" s="47">
-        <f>C74-C77-C78</f>
-        <v>779000</v>
-      </c>
-      <c r="D75" s="48"/>
-      <c r="E75" s="35">
-        <f>C75/C73*100</f>
-        <v>83.73150423762138</v>
-      </c>
-    </row>
-    <row r="76" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B76" s="34" t="s">
-        <v>26</v>
-      </c>
-      <c r="C76" s="49">
-        <f>C73-C75</f>
-        <v>151354.71784822864</v>
-      </c>
-      <c r="D76" s="49"/>
-      <c r="E76" s="35">
-        <f>100-E75</f>
-        <v>16.26849576237862</v>
-      </c>
-    </row>
-    <row r="77" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B77" s="34" t="s">
-        <v>23</v>
-      </c>
-      <c r="C77" s="45">
-        <f>C74*0.03</f>
-        <v>24600</v>
-      </c>
-      <c r="D77" s="46"/>
-      <c r="E77" s="35">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="78" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="34" t="s">
-        <v>24</v>
-      </c>
-      <c r="C78" s="45">
-        <f>C74*0.02</f>
-        <v>16400</v>
-      </c>
-      <c r="D78" s="46"/>
-      <c r="E78" s="35">
-        <v>2</v>
-      </c>
-      <c r="Q78"/>
+      <c r="C59" s="53">
+        <f>J57</f>
+        <v>985560.96692826762</v>
+      </c>
+      <c r="D59" s="54"/>
+      <c r="E59" s="35"/>
+      <c r="F59" s="33"/>
+      <c r="G59" s="36"/>
+      <c r="H59" s="33"/>
+      <c r="I59" s="37"/>
+      <c r="J59" s="38"/>
+      <c r="K59" s="39"/>
+      <c r="Q59" s="5"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="10">
+    <mergeCell ref="C59:D59"/>
     <mergeCell ref="A7:F7"/>
     <mergeCell ref="H7:K7"/>
     <mergeCell ref="A1:K1"/>
@@ -2771,12 +2409,6 @@
     <mergeCell ref="A5:K5"/>
     <mergeCell ref="A6:F6"/>
     <mergeCell ref="H6:K6"/>
-    <mergeCell ref="C78:D78"/>
-    <mergeCell ref="C73:D73"/>
-    <mergeCell ref="C74:D74"/>
-    <mergeCell ref="C75:D75"/>
-    <mergeCell ref="C76:D76"/>
-    <mergeCell ref="C77:D77"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2793,7 +2425,7 @@
   <sheetData>
     <row r="8" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B8" s="6" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="C8" s="6"/>
       <c r="D8" s="6"/>
@@ -2801,16 +2433,16 @@
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B9" s="5" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.25">
